--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1115,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1246,7 +1254,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2279-145-CM25</t>
+          <t>1213444-116-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1266,42 +1274,46 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>71.328.600-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMMERCE CHILE SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.037.031-0</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>26601.45</v>
+        <v>51239.66</v>
       </c>
     </row>
     <row r="15">
@@ -1355,7 +1367,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1368,7 +1384,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1213444-116-CM25</t>
+          <t>2279-145-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,42 +1404,46 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>COMMERCE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>77.037.031-0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>O'Higgins</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>51239.66</v>
+        <v>26601.45</v>
       </c>
     </row>
     <row r="17">
@@ -1660,7 +1680,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1745,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1734,7 +1762,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1233623-86-CM25</t>
+          <t>948354-339-SE25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1777,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,17 +1787,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1782,14 +1810,18 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5890.87</v>
+        <v>13720.45</v>
       </c>
     </row>
     <row r="23">
@@ -1843,7 +1875,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1917,7 +1953,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057417-15445-CM25</t>
+          <t>1233623-86-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1968,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,43 +1978,47 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6610.7</v>
+        <v>5890.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5153-764-CM25</t>
+          <t>1057417-15445-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,53 +2033,57 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>57396.1</v>
+        <v>6610.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5520-408-CM25</t>
+          <t>5153-764-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2098,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2079,12 +2123,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MUEBLES ANDROMEDA DOS SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.285.439-0</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2138,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7435.14</v>
+        <v>57396.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1655-903-CM25</t>
+          <t>5520-408-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,17 +2164,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.608.605-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,28 +2184,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>OFISILLAS CHILE SPA</t>
+          <t>MUEBLES ANDROMEDA DOS SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.855.435-8</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>77.285.439-0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>7817.76</v>
+        <v>7435.14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>692277-20-CM25</t>
+          <t>1655-903-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,12 +2234,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>61.608.605-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,28 +2249,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>31266.49</v>
+        <v>7817.76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>867990-294-CM25</t>
+          <t>692277-20-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,22 +2289,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2314,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>JAIME DEIK Y CIA. LIMITADA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.450.030-k</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,7 +2329,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>38164.07</v>
+        <v>31266.49</v>
       </c>
     </row>
     <row r="31">
@@ -2331,7 +2383,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2448,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2405,7 +2465,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>696954-10-CM25</t>
+          <t>867990-294-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2480,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,27 +2490,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>JAIME DEIK Y CIA. LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>76.450.030-k</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,6 +2520,71 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
+        <v>38164.07</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>696954-10-CM25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>23451.74</v>
       </c>
     </row>
